--- a/Result/30-05-25/S&P500stock_30-05-25period252RS90.xlsx
+++ b/Result/30-05-25/S&P500stock_30-05-25period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/30-05-25/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A6CBA6-EB55-4342-AC56-C430CC14BD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -364,12 +370,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -377,8 +383,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -424,17 +437,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -472,7 +493,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -506,6 +527,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -540,9 +562,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -715,9 +738,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:42">
       <c r="A1" s="1" t="s">
@@ -852,10 +875,10 @@
         <v>42</v>
       </c>
       <c r="B2">
-        <v>92.44532803180915</v>
+        <v>92.445328031809154</v>
       </c>
       <c r="C2">
-        <v>77.33598409542743</v>
+        <v>77.335984095427435</v>
       </c>
       <c r="D2">
         <v>366</v>
@@ -867,37 +890,37 @@
         <v>156.74</v>
       </c>
       <c r="G2">
-        <v>0.3475088948878193</v>
+        <v>0.34750889488781928</v>
       </c>
       <c r="H2">
-        <v>0.779214917004616</v>
+        <v>0.77921491700461598</v>
       </c>
       <c r="I2">
         <v>1.74</v>
       </c>
       <c r="J2">
-        <v>-0.3505213843736795</v>
+        <v>-0.35052138437367952</v>
       </c>
       <c r="K2">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="L2">
-        <v>-0.45415724956112</v>
+        <v>-0.45415724956112002</v>
       </c>
       <c r="M2">
-        <v>157.6899993896484</v>
+        <v>157.68999938964839</v>
       </c>
       <c r="N2">
         <v>162.4955009460449</v>
       </c>
       <c r="O2">
-        <v>155.4422012329102</v>
+        <v>155.44220123291021</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>140.4340502548218</v>
+        <v>140.43405025482181</v>
       </c>
       <c r="R2">
         <v>0.97</v>
@@ -906,7 +929,7 @@
         <v>1.05</v>
       </c>
       <c r="U2">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -936,7 +959,7 @@
         <v>154.35</v>
       </c>
       <c r="AE2">
-        <v>4.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="AF2">
         <v>24.14</v>
@@ -966,10 +989,10 @@
         <v>3.24</v>
       </c>
       <c r="AO2">
-        <v>67.01000000000001</v>
+        <v>67.010000000000005</v>
       </c>
       <c r="AP2">
-        <v>79.92134138933815</v>
+        <v>79.921341389338153</v>
       </c>
     </row>
     <row r="3" spans="1:42">
@@ -977,10 +1000,10 @@
         <v>43</v>
       </c>
       <c r="B3">
-        <v>98.40954274353876</v>
+        <v>98.409542743538765</v>
       </c>
       <c r="C3">
-        <v>74.35387673956262</v>
+        <v>74.353876739562622</v>
       </c>
       <c r="D3">
         <v>144</v>
@@ -1007,22 +1030,22 @@
         <v>3.67</v>
       </c>
       <c r="L3">
-        <v>0.6764451860551706</v>
+        <v>0.67644518605517057</v>
       </c>
       <c r="M3">
         <v>204.6159973144531</v>
       </c>
       <c r="N3">
-        <v>198.0659996032715</v>
+        <v>198.06599960327151</v>
       </c>
       <c r="O3">
-        <v>189.5118005371094</v>
+        <v>189.51180053710939</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>170.6769499969483</v>
+        <v>170.67694999694831</v>
       </c>
       <c r="R3">
         <v>1.03</v>
@@ -1031,7 +1054,7 @@
         <v>1.05</v>
       </c>
       <c r="U3">
-        <v>8.888888888888888</v>
+        <v>8.8888888888888875</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -1043,19 +1066,19 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>99.31999999999999</v>
+        <v>99.32</v>
       </c>
       <c r="Z3">
         <v>215.24</v>
       </c>
       <c r="AA3">
-        <v>87.54000000000001</v>
+        <v>87.54</v>
       </c>
       <c r="AB3" t="s">
         <v>68</v>
       </c>
       <c r="AC3">
-        <v>647.42</v>
+        <v>647.41999999999996</v>
       </c>
       <c r="AD3">
         <v>881.48</v>
@@ -1067,10 +1090,10 @@
         <v>202.63</v>
       </c>
       <c r="AG3">
-        <v>-533.33</v>
+        <v>-533.33000000000004</v>
       </c>
       <c r="AH3">
-        <v>84.20999999999999</v>
+        <v>84.21</v>
       </c>
       <c r="AI3" t="s">
         <v>70</v>
@@ -1094,7 +1117,7 @@
         <v>128.21</v>
       </c>
       <c r="AP3">
-        <v>73.00737738126952</v>
+        <v>73.007377381269521</v>
       </c>
     </row>
     <row r="4" spans="1:42">
@@ -1102,10 +1125,10 @@
         <v>44</v>
       </c>
       <c r="B4">
-        <v>99.80119284294234</v>
+        <v>99.801192842942342</v>
       </c>
       <c r="C4">
-        <v>99.60238568588468</v>
+        <v>99.602385685884684</v>
       </c>
       <c r="D4">
         <v>181</v>
@@ -1117,16 +1140,16 @@
         <v>471.17</v>
       </c>
       <c r="G4">
-        <v>1.462423872464704</v>
+        <v>1.4624238724647041</v>
       </c>
       <c r="H4">
-        <v>1.819468678059116</v>
+        <v>1.8194686780591161</v>
       </c>
       <c r="I4">
         <v>2.13</v>
       </c>
       <c r="J4">
-        <v>0.002170411048753598</v>
+        <v>2.1704110487535981E-3</v>
       </c>
       <c r="K4">
         <v>4.08</v>
@@ -1135,28 +1158,28 @@
         <v>1.069281625548967</v>
       </c>
       <c r="M4">
-        <v>470.1800109863281</v>
+        <v>470.18001098632811</v>
       </c>
       <c r="N4">
-        <v>430.9705047607422</v>
+        <v>430.97050476074219</v>
       </c>
       <c r="O4">
-        <v>368.0822021484375</v>
+        <v>368.08220214843749</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>318.7565501403809</v>
+        <v>318.75655014038091</v>
       </c>
       <c r="R4">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="S4">
         <v>1.17</v>
       </c>
       <c r="U4">
-        <v>8.888888888888889</v>
+        <v>8.8888888888888893</v>
       </c>
       <c r="V4" t="b">
         <v>0</v>
@@ -1183,7 +1206,7 @@
         <v>1154.21</v>
       </c>
       <c r="AD4">
-        <v>293.21</v>
+        <v>293.20999999999998</v>
       </c>
       <c r="AE4">
         <v>22.02</v>
@@ -1219,7 +1242,7 @@
         <v>1.77</v>
       </c>
       <c r="AP4">
-        <v>69.20253705096538</v>
+        <v>69.202537050965375</v>
       </c>
     </row>
     <row r="5" spans="1:42">
@@ -1227,10 +1250,10 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>97.61431411530815</v>
+        <v>97.614314115308147</v>
       </c>
       <c r="C5">
-        <v>97.21669980119285</v>
+        <v>97.216699801192846</v>
       </c>
       <c r="D5">
         <v>23</v>
@@ -1242,16 +1265,16 @@
         <v>241.97</v>
       </c>
       <c r="G5">
-        <v>0.5079719737555444</v>
+        <v>0.50797197375554437</v>
       </c>
       <c r="H5">
-        <v>2.079336112830337</v>
+        <v>2.0793361128303371</v>
       </c>
       <c r="I5">
         <v>2.09</v>
       </c>
       <c r="J5">
-        <v>-0.03400310643047035</v>
+        <v>-3.4003106430470352E-2</v>
       </c>
       <c r="K5">
         <v>4.18</v>
@@ -1260,13 +1283,13 @@
         <v>1.16509539127916</v>
       </c>
       <c r="M5">
-        <v>235.2599975585937</v>
+        <v>235.25999755859371</v>
       </c>
       <c r="N5">
-        <v>221.9134986877442</v>
+        <v>221.91349868774421</v>
       </c>
       <c r="O5">
-        <v>194.9201992797852</v>
+        <v>194.92019927978521</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
@@ -1278,10 +1301,10 @@
         <v>1.06</v>
       </c>
       <c r="S5">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="U5">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1305,10 +1328,10 @@
         <v>13.91</v>
       </c>
       <c r="AC5">
-        <v>35.87</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="AD5">
-        <v>301.09</v>
+        <v>301.08999999999997</v>
       </c>
       <c r="AE5">
         <v>14.85</v>
@@ -1335,7 +1358,7 @@
         <v>114</v>
       </c>
       <c r="AM5">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="AN5">
         <v>6.17</v>
@@ -1344,7 +1367,7 @@
         <v>183.03</v>
       </c>
       <c r="AP5">
-        <v>42.30600540907148</v>
+        <v>42.306005409071481</v>
       </c>
     </row>
     <row r="6" spans="1:42">
@@ -1352,10 +1375,10 @@
         <v>46</v>
       </c>
       <c r="B6">
-        <v>97.21669980119285</v>
+        <v>97.216699801192846</v>
       </c>
       <c r="C6">
-        <v>37.77335984095427</v>
+        <v>37.773359840954271</v>
       </c>
       <c r="D6">
         <v>106</v>
@@ -1367,10 +1390,10 @@
         <v>111.11</v>
       </c>
       <c r="G6">
-        <v>0.6825169126721853</v>
+        <v>0.68251691267218528</v>
       </c>
       <c r="H6">
-        <v>0.2992380276300516</v>
+        <v>0.29923802763005158</v>
       </c>
       <c r="I6">
         <v>2.73</v>
@@ -1382,7 +1405,7 @@
         <v>2.11</v>
       </c>
       <c r="L6">
-        <v>-0.8182495593358581</v>
+        <v>-0.81824955933585808</v>
       </c>
       <c r="M6">
         <v>108.55</v>
@@ -1397,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>95.16374980926514</v>
+        <v>95.163749809265141</v>
       </c>
       <c r="R6">
         <v>1.05</v>
@@ -1427,10 +1450,10 @@
         <v>138.21</v>
       </c>
       <c r="AB6">
-        <v>-38.13</v>
+        <v>-38.130000000000003</v>
       </c>
       <c r="AC6">
-        <v>73.01000000000001</v>
+        <v>73.010000000000005</v>
       </c>
       <c r="AD6">
         <v>131.24</v>
@@ -1469,7 +1492,7 @@
         <v>56.09</v>
       </c>
       <c r="AP6">
-        <v>39.84029341800806</v>
+        <v>39.840293418008059</v>
       </c>
     </row>
     <row r="7" spans="1:42">
@@ -1477,10 +1500,10 @@
         <v>47</v>
       </c>
       <c r="B7">
-        <v>97.4155069582505</v>
+        <v>97.415506958250504</v>
       </c>
       <c r="C7">
-        <v>87.47514910536779</v>
+        <v>87.475149105367791</v>
       </c>
       <c r="D7">
         <v>317</v>
@@ -1492,7 +1515,7 @@
         <v>254.44</v>
       </c>
       <c r="G7">
-        <v>0.5280693204040149</v>
+        <v>0.52806932040401489</v>
       </c>
       <c r="H7">
         <v>1.623199335837237</v>
@@ -1501,7 +1524,7 @@
         <v>2.48</v>
       </c>
       <c r="J7">
-        <v>0.318688688991963</v>
+        <v>0.31868868899196301</v>
       </c>
       <c r="K7">
         <v>3.88</v>
@@ -1510,10 +1533,10 @@
         <v>0.8776540940885782</v>
       </c>
       <c r="M7">
-        <v>247.8599975585938</v>
+        <v>247.85999755859379</v>
       </c>
       <c r="N7">
-        <v>241.3154975891113</v>
+        <v>241.31549758911129</v>
       </c>
       <c r="O7">
         <v>219.0007986450195</v>
@@ -1528,7 +1551,7 @@
         <v>1.03</v>
       </c>
       <c r="S7">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="U7">
         <v>3.888888888888888</v>
@@ -1543,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>130.08</v>
+        <v>130.08000000000001</v>
       </c>
       <c r="Z7">
         <v>277.08</v>
       </c>
       <c r="AA7">
-        <v>69.09999999999999</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="AB7">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AC7">
         <v>29.85</v>
@@ -1617,16 +1640,16 @@
         <v>122.32</v>
       </c>
       <c r="G8">
-        <v>4.598691729165075</v>
+        <v>4.5986917291650746</v>
       </c>
       <c r="H8">
-        <v>2.163437009161792</v>
+        <v>2.1634370091617918</v>
       </c>
       <c r="I8">
         <v>4.37</v>
       </c>
       <c r="J8">
-        <v>2.027887389885293</v>
+        <v>2.0278873898852932</v>
       </c>
       <c r="K8">
         <v>5.39</v>
@@ -1638,7 +1661,7 @@
         <v>123.0139999389648</v>
       </c>
       <c r="N8">
-        <v>122.0994998931885</v>
+        <v>122.09949989318849</v>
       </c>
       <c r="O8">
         <v>104.7841998291016</v>
@@ -1647,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>72.98995003700256</v>
+        <v>72.989950037002558</v>
       </c>
       <c r="R8">
         <v>1.01</v>
@@ -1719,7 +1742,7 @@
         <v>104.35</v>
       </c>
       <c r="AP8">
-        <v>33.4795741343371</v>
+        <v>33.479574134337099</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -1730,7 +1753,7 @@
         <v>99.40357852882704</v>
       </c>
       <c r="C9">
-        <v>98.40954274353876</v>
+        <v>98.409542743538765</v>
       </c>
       <c r="D9">
         <v>235</v>
@@ -1742,7 +1765,7 @@
         <v>170.09</v>
       </c>
       <c r="G9">
-        <v>0.8520700291110015</v>
+        <v>0.85207002911100149</v>
       </c>
       <c r="H9">
         <v>1.334600917238741</v>
@@ -1751,19 +1774,19 @@
         <v>1.82</v>
       </c>
       <c r="J9">
-        <v>-0.2781743494152316</v>
+        <v>-0.27817434941523161</v>
       </c>
       <c r="K9">
         <v>3.07</v>
       </c>
       <c r="L9">
-        <v>0.1015625916740057</v>
+        <v>0.10156259167400571</v>
       </c>
       <c r="M9">
-        <v>167.6399993896484</v>
+        <v>167.63999938964841</v>
       </c>
       <c r="N9">
-        <v>160.7690010070801</v>
+        <v>160.76900100708011</v>
       </c>
       <c r="O9">
         <v>141.5058004760742</v>
@@ -1778,7 +1801,7 @@
         <v>1.04</v>
       </c>
       <c r="S9">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="U9">
         <v>12.22222222222222</v>
@@ -1814,7 +1837,7 @@
         <v>28.29</v>
       </c>
       <c r="AF9">
-        <v>-4.94</v>
+        <v>-4.9400000000000004</v>
       </c>
       <c r="AG9">
         <v>24.62</v>
@@ -1844,7 +1867,7 @@
         <v>3.59</v>
       </c>
       <c r="AP9">
-        <v>32.2611999958575</v>
+        <v>32.261199995857503</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -1852,10 +1875,10 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>98.01192842942345</v>
+        <v>98.011928429423449</v>
       </c>
       <c r="C10">
-        <v>99.80119284294234</v>
+        <v>99.801192842942342</v>
       </c>
       <c r="D10">
         <v>207</v>
@@ -1867,40 +1890,40 @@
         <v>154.47</v>
       </c>
       <c r="G10">
-        <v>0.6696927862501423</v>
+        <v>0.66969278625014228</v>
       </c>
       <c r="H10">
-        <v>1.692019882422673</v>
+        <v>1.6920198824226731</v>
       </c>
       <c r="I10">
         <v>6.01</v>
       </c>
       <c r="J10">
-        <v>3.511001606533474</v>
+        <v>3.5110016065334739</v>
       </c>
       <c r="K10">
-        <v>4.98</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="L10">
         <v>1.931605517120714</v>
       </c>
       <c r="M10">
-        <v>156.1100006103516</v>
+        <v>156.11000061035159</v>
       </c>
       <c r="N10">
-        <v>142.7325004577637</v>
+        <v>142.73250045776371</v>
       </c>
       <c r="O10">
-        <v>116.0726000976562</v>
+        <v>116.07260009765621</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>99.05225017547608</v>
+        <v>99.052250175476075</v>
       </c>
       <c r="R10">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="S10">
         <v>1.23</v>
@@ -1969,7 +1992,7 @@
         <v>10.75</v>
       </c>
       <c r="AP10">
-        <v>32.01393714327553</v>
+        <v>32.013937143275527</v>
       </c>
     </row>
     <row r="11" spans="1:42">
@@ -1977,10 +2000,10 @@
         <v>51</v>
       </c>
       <c r="B11">
-        <v>98.80715705765407</v>
+        <v>98.807157057654067</v>
       </c>
       <c r="C11">
-        <v>36.58051689860835</v>
+        <v>36.580516898608352</v>
       </c>
       <c r="D11">
         <v>159</v>
@@ -1992,43 +2015,43 @@
         <v>78.44</v>
       </c>
       <c r="G11">
-        <v>0.7630729550860419</v>
+        <v>0.76307295508604189</v>
       </c>
       <c r="H11">
-        <v>1.200888297525177</v>
+        <v>1.2008882975251769</v>
       </c>
       <c r="I11">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="J11">
-        <v>0.2915585508825452</v>
+        <v>0.29155855088254518</v>
       </c>
       <c r="K11">
         <v>3.26</v>
       </c>
       <c r="L11">
-        <v>0.2836087465613745</v>
+        <v>0.28360874656137453</v>
       </c>
       <c r="M11">
-        <v>79.12400054931641</v>
+        <v>79.124000549316406</v>
       </c>
       <c r="N11">
-        <v>78.79800033569336</v>
+        <v>78.798000335693359</v>
       </c>
       <c r="O11">
-        <v>72.45820022583008</v>
+        <v>72.458200225830083</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
       </c>
       <c r="Q11">
-        <v>62.33049995422363</v>
+        <v>62.330499954223633</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -2043,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>35.23</v>
+        <v>35.229999999999997</v>
       </c>
       <c r="Z11">
-        <v>90.84999999999999</v>
+        <v>90.85</v>
       </c>
       <c r="AA11">
         <v>16.7</v>
@@ -2061,10 +2084,10 @@
         <v>59.68</v>
       </c>
       <c r="AE11">
-        <v>40.27</v>
+        <v>40.270000000000003</v>
       </c>
       <c r="AF11">
-        <v>74.06999999999999</v>
+        <v>74.069999999999993</v>
       </c>
       <c r="AG11">
         <v>17.39</v>
@@ -2094,7 +2117,7 @@
         <v>28.3</v>
       </c>
       <c r="AP11">
-        <v>29.92107218993308</v>
+        <v>29.921072189933081</v>
       </c>
     </row>
     <row r="12" spans="1:42">
@@ -2102,10 +2125,10 @@
         <v>52</v>
       </c>
       <c r="B12">
-        <v>96.02385685884693</v>
+        <v>96.023856858846926</v>
       </c>
       <c r="C12">
-        <v>95.42743538767395</v>
+        <v>95.427435387673953</v>
       </c>
       <c r="D12">
         <v>338</v>
@@ -2117,37 +2140,37 @@
         <v>153.99</v>
       </c>
       <c r="G12">
-        <v>0.5586248904844393</v>
+        <v>0.55862489048443931</v>
       </c>
       <c r="H12">
-        <v>0.4344975432106585</v>
+        <v>0.43449754321065848</v>
       </c>
       <c r="I12">
         <v>1.56</v>
       </c>
       <c r="J12">
-        <v>-0.5133022130301871</v>
+        <v>-0.51330221303018708</v>
       </c>
       <c r="K12">
         <v>1.63</v>
       </c>
       <c r="L12">
-        <v>-1.27815563484079</v>
+        <v>-1.2781556348407901</v>
       </c>
       <c r="M12">
-        <v>153.4080017089844</v>
+        <v>153.40800170898439</v>
       </c>
       <c r="N12">
-        <v>151.4090003967285</v>
+        <v>151.40900039672849</v>
       </c>
       <c r="O12">
-        <v>141.0106001281738</v>
+        <v>141.01060012817379</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>124.1547499465942</v>
+        <v>124.15474994659419</v>
       </c>
       <c r="R12">
         <v>1.01</v>
@@ -2156,7 +2179,7 @@
         <v>1.07</v>
       </c>
       <c r="U12">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -2192,7 +2215,7 @@
         <v>-3.51</v>
       </c>
       <c r="AH12">
-        <v>76.29000000000001</v>
+        <v>76.290000000000006</v>
       </c>
       <c r="AI12" t="s">
         <v>76</v>
@@ -2210,13 +2233,13 @@
         <v>6.42</v>
       </c>
       <c r="AN12">
-        <v>8.640000000000001</v>
+        <v>8.64</v>
       </c>
       <c r="AO12">
         <v>34.58</v>
       </c>
       <c r="AP12">
-        <v>28.80689381559855</v>
+        <v>28.806893815598549</v>
       </c>
     </row>
     <row r="13" spans="1:42">
@@ -2224,10 +2247,10 @@
         <v>53</v>
       </c>
       <c r="B13">
-        <v>98.60834990059642</v>
+        <v>98.608349900596423</v>
       </c>
       <c r="C13">
-        <v>95.22862823061629</v>
+        <v>95.228628230616295</v>
       </c>
       <c r="D13">
         <v>250</v>
@@ -2236,19 +2259,19 @@
         <v>193</v>
       </c>
       <c r="F13">
-        <v>1184.86</v>
+        <v>1184.8599999999999</v>
       </c>
       <c r="G13">
-        <v>0.7135491022757254</v>
+        <v>0.71354910227572543</v>
       </c>
       <c r="H13">
-        <v>0.9749173884563727</v>
+        <v>0.97491738845637266</v>
       </c>
       <c r="I13">
         <v>1.47</v>
       </c>
       <c r="J13">
-        <v>-0.594692627358441</v>
+        <v>-0.59469262735844097</v>
       </c>
       <c r="K13">
         <v>2.73</v>
@@ -2263,22 +2286,22 @@
         <v>1166.366998291016</v>
       </c>
       <c r="O13">
-        <v>1052.542999267578</v>
+        <v>1052.5429992675779</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>889.0413970947266</v>
+        <v>889.04139709472656</v>
       </c>
       <c r="R13">
         <v>1.03</v>
       </c>
       <c r="S13">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="U13">
-        <v>9.444444444444443</v>
+        <v>9.4444444444444429</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
@@ -2293,10 +2316,10 @@
         <v>587.04</v>
       </c>
       <c r="Z13">
-        <v>1215.91</v>
+        <v>1215.9100000000001</v>
       </c>
       <c r="AA13">
-        <v>514.3200000000001</v>
+        <v>514.32000000000005</v>
       </c>
       <c r="AB13">
         <v>36.85</v>
@@ -2308,7 +2331,7 @@
         <v>25.26</v>
       </c>
       <c r="AE13">
-        <v>40.84</v>
+        <v>40.840000000000003</v>
       </c>
       <c r="AF13">
         <v>-20.83</v>
@@ -2349,10 +2372,10 @@
         <v>54</v>
       </c>
       <c r="B14">
-        <v>92.6441351888668</v>
+        <v>92.644135188866798</v>
       </c>
       <c r="C14">
-        <v>95.82504970178927</v>
+        <v>95.825049701789268</v>
       </c>
       <c r="D14">
         <v>97</v>
@@ -2364,49 +2387,49 @@
         <v>244.16</v>
       </c>
       <c r="G14">
-        <v>0.3167779216382581</v>
+        <v>0.31677792163825808</v>
       </c>
       <c r="H14">
-        <v>1.207673523773865</v>
+        <v>1.2076735237738649</v>
       </c>
       <c r="I14">
         <v>1.2</v>
       </c>
       <c r="J14">
-        <v>-0.8388638703432025</v>
+        <v>-0.83886387034320253</v>
       </c>
       <c r="K14">
         <v>2.77</v>
       </c>
       <c r="L14">
-        <v>-0.1858787055165766</v>
+        <v>-0.18587870551657659</v>
       </c>
       <c r="M14">
-        <v>238.5339996337891</v>
+        <v>238.53399963378911</v>
       </c>
       <c r="N14">
-        <v>224.4955001831055</v>
+        <v>224.49550018310549</v>
       </c>
       <c r="O14">
-        <v>205.6111993408203</v>
+        <v>205.61119934082029</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>188.8057002258301</v>
+        <v>188.80570022583009</v>
       </c>
       <c r="R14">
         <v>1.06</v>
       </c>
       <c r="S14">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="T14" t="s">
         <v>67</v>
       </c>
       <c r="U14">
-        <v>9.444444444444443</v>
+        <v>9.4444444444444429</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
@@ -2418,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>150.2</v>
+        <v>150.19999999999999</v>
       </c>
       <c r="Z14">
         <v>246</v>
@@ -2469,7 +2492,7 @@
         <v>-17.48</v>
       </c>
       <c r="AP14">
-        <v>26.26201498846465</v>
+        <v>26.262014988464649</v>
       </c>
     </row>
     <row r="15" spans="1:42">
@@ -2477,10 +2500,10 @@
         <v>55</v>
       </c>
       <c r="B15">
-        <v>94.23459244532803</v>
+        <v>94.234592445328033</v>
       </c>
       <c r="C15">
-        <v>67.9920477137177</v>
+        <v>67.992047713717696</v>
       </c>
       <c r="D15">
         <v>174</v>
@@ -2489,40 +2512,40 @@
         <v>173</v>
       </c>
       <c r="F15">
-        <v>89.06999999999999</v>
+        <v>89.07</v>
       </c>
       <c r="G15">
-        <v>0.4245873533637519</v>
+        <v>0.42458735336375192</v>
       </c>
       <c r="H15">
-        <v>0.8876927417826305</v>
+        <v>0.88769274178263047</v>
       </c>
       <c r="I15">
         <v>0.91</v>
       </c>
       <c r="J15">
-        <v>-1.101121872067576</v>
+        <v>-1.1011218720675759</v>
       </c>
       <c r="K15">
         <v>2.16</v>
       </c>
       <c r="L15">
-        <v>-0.7703426764707607</v>
+        <v>-0.77034267647076071</v>
       </c>
       <c r="M15">
-        <v>89.27400054931641</v>
+        <v>89.274000549316412</v>
       </c>
       <c r="N15">
-        <v>87.08150062561035</v>
+        <v>87.081500625610346</v>
       </c>
       <c r="O15">
-        <v>82.67420028686523</v>
+        <v>82.674200286865229</v>
       </c>
       <c r="P15" t="b">
         <v>1</v>
       </c>
       <c r="Q15">
-        <v>78.74865005493164</v>
+        <v>78.748650054931645</v>
       </c>
       <c r="R15">
         <v>1.03</v>
@@ -2531,7 +2554,7 @@
         <v>1.05</v>
       </c>
       <c r="U15">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2594,7 +2617,7 @@
         <v>6.18</v>
       </c>
       <c r="AP15">
-        <v>24.46794116062563</v>
+        <v>24.467941160625632</v>
       </c>
     </row>
     <row r="16" spans="1:42">
@@ -2602,10 +2625,10 @@
         <v>56</v>
       </c>
       <c r="B16">
-        <v>94.83101391650099</v>
+        <v>94.831013916500993</v>
       </c>
       <c r="C16">
-        <v>49.10536779324055</v>
+        <v>49.105367793240553</v>
       </c>
       <c r="D16">
         <v>262</v>
@@ -2617,37 +2640,37 @@
         <v>153.07</v>
       </c>
       <c r="G16">
-        <v>0.4594518904062292</v>
+        <v>0.45945189040622919</v>
       </c>
       <c r="H16">
-        <v>0.3400995496719237</v>
+        <v>0.34009954967192368</v>
       </c>
       <c r="I16">
         <v>1.39</v>
       </c>
       <c r="J16">
-        <v>-0.6670396623168889</v>
+        <v>-0.66703966231688894</v>
       </c>
       <c r="K16">
         <v>1.68</v>
       </c>
       <c r="L16">
-        <v>-1.230248751975693</v>
+        <v>-1.2302487519756931</v>
       </c>
       <c r="M16">
-        <v>150.6619995117188</v>
+        <v>150.66199951171879</v>
       </c>
       <c r="N16">
-        <v>149.2324989318848</v>
+        <v>149.23249893188481</v>
       </c>
       <c r="O16">
-        <v>148.1581991577148</v>
+        <v>148.15819915771479</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>136.6086994552612</v>
+        <v>136.60869945526119</v>
       </c>
       <c r="R16">
         <v>1.01</v>
@@ -2656,7 +2679,7 @@
         <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2671,7 +2694,7 @@
         <v>99.95</v>
       </c>
       <c r="Z16">
-        <v>158.55</v>
+        <v>158.55000000000001</v>
       </c>
       <c r="AA16">
         <v>100.1</v>
@@ -2719,7 +2742,7 @@
         <v>2.25</v>
       </c>
       <c r="AP16">
-        <v>24.21957351130338</v>
+        <v>24.219573511303381</v>
       </c>
     </row>
     <row r="17" spans="1:42">
@@ -2730,7 +2753,7 @@
         <v>96.22266401590457</v>
       </c>
       <c r="C17">
-        <v>82.90258449304176</v>
+        <v>82.902584493041758</v>
       </c>
       <c r="D17">
         <v>404</v>
@@ -2742,7 +2765,7 @@
         <v>277.73</v>
       </c>
       <c r="G17">
-        <v>0.3847606975168402</v>
+        <v>0.38476069751684022</v>
       </c>
       <c r="H17">
         <v>1.39543282947168</v>
@@ -2766,19 +2789,19 @@
         <v>262.5780029296875</v>
       </c>
       <c r="O17">
-        <v>233.4268005371094</v>
+        <v>233.42680053710939</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>221.5052503204346</v>
+        <v>221.50525032043461</v>
       </c>
       <c r="R17">
         <v>1.07</v>
       </c>
       <c r="S17">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -2844,7 +2867,7 @@
         <v>14.61</v>
       </c>
       <c r="AP17">
-        <v>20.32918876689114</v>
+        <v>20.329188766891139</v>
       </c>
     </row>
     <row r="18" spans="1:42">
@@ -2852,10 +2875,10 @@
         <v>58</v>
       </c>
       <c r="B18">
-        <v>97.81312127236581</v>
+        <v>97.813121272365805</v>
       </c>
       <c r="C18">
-        <v>90.05964214711729</v>
+        <v>90.059642147117287</v>
       </c>
       <c r="D18">
         <v>133</v>
@@ -2867,7 +2890,7 @@
         <v>177.87</v>
       </c>
       <c r="G18">
-        <v>0.7366793668973658</v>
+        <v>0.73667936689736579</v>
       </c>
       <c r="H18">
         <v>0.1321512913048612</v>
@@ -2876,7 +2899,7 @@
         <v>1.33</v>
       </c>
       <c r="J18">
-        <v>-0.7212999385357246</v>
+        <v>-0.72129993853572461</v>
       </c>
       <c r="K18">
         <v>1.59</v>
@@ -2885,10 +2908,10 @@
         <v>-1.316481141132867</v>
       </c>
       <c r="M18">
-        <v>177.8619964599609</v>
+        <v>177.86199645996089</v>
       </c>
       <c r="N18">
-        <v>172.4369995117187</v>
+        <v>172.43699951171871</v>
       </c>
       <c r="O18">
         <v>164.1021994018555</v>
@@ -2906,7 +2929,7 @@
         <v>1.05</v>
       </c>
       <c r="U18">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="V18" t="b">
         <v>0</v>
@@ -2918,13 +2941,13 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>98.93000000000001</v>
+        <v>98.93</v>
       </c>
       <c r="Z18">
         <v>179.83</v>
       </c>
       <c r="AA18">
-        <v>278.29</v>
+        <v>278.29000000000002</v>
       </c>
       <c r="AB18">
         <v>-0.38</v>
@@ -2969,7 +2992,7 @@
         <v>14.1</v>
       </c>
       <c r="AP18">
-        <v>18.44213091965378</v>
+        <v>18.442130919653781</v>
       </c>
     </row>
     <row r="19" spans="1:42">
@@ -2977,10 +3000,10 @@
         <v>59</v>
       </c>
       <c r="B19">
-        <v>96.81908548707754</v>
+        <v>96.819085487077544</v>
       </c>
       <c r="C19">
-        <v>51.88866799204771</v>
+        <v>51.888667992047708</v>
       </c>
       <c r="D19">
         <v>491</v>
@@ -2989,10 +3012,10 @@
         <v>487</v>
       </c>
       <c r="F19">
-        <v>280.59</v>
+        <v>280.58999999999997</v>
       </c>
       <c r="G19">
-        <v>0.5517390162574869</v>
+        <v>0.55173901625748689</v>
       </c>
       <c r="H19">
         <v>1.009881157670407</v>
@@ -3001,28 +3024,28 @@
         <v>1.26</v>
       </c>
       <c r="J19">
-        <v>-0.7846035941243665</v>
+        <v>-0.78460359412436653</v>
       </c>
       <c r="K19">
         <v>2.33</v>
       </c>
       <c r="L19">
-        <v>-0.6074592747294307</v>
+        <v>-0.60745927472943073</v>
       </c>
       <c r="M19">
-        <v>283.4100036621094</v>
+        <v>283.41000366210938</v>
       </c>
       <c r="N19">
-        <v>278.2975051879883</v>
+        <v>278.29750518798829</v>
       </c>
       <c r="O19">
-        <v>268.7080010986328</v>
+        <v>268.70800109863279</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>251.3058505249024</v>
+        <v>251.30585052490241</v>
       </c>
       <c r="R19">
         <v>1.02</v>
@@ -3094,7 +3117,7 @@
         <v>47.51</v>
       </c>
       <c r="AP19">
-        <v>14.23446707881627</v>
+        <v>14.234467078816269</v>
       </c>
     </row>
     <row r="20" spans="1:42">
@@ -3102,7 +3125,7 @@
         <v>60</v>
       </c>
       <c r="B20">
-        <v>97.01789264413519</v>
+        <v>97.017892644135188</v>
       </c>
       <c r="C20">
         <v>33.79721669980119</v>
@@ -3117,7 +3140,7 @@
         <v>102.04</v>
       </c>
       <c r="G20">
-        <v>0.5967913324286258</v>
+        <v>0.59679133242862581</v>
       </c>
       <c r="H20">
         <v>1.063811008714892</v>
@@ -3126,13 +3149,13 @@
         <v>2.65</v>
       </c>
       <c r="J20">
-        <v>0.4724261382786646</v>
+        <v>0.47242613827866459</v>
       </c>
       <c r="K20">
         <v>3.23</v>
       </c>
       <c r="L20">
-        <v>0.2548646168423164</v>
+        <v>0.25486461684231643</v>
       </c>
       <c r="M20">
         <v>103.6140014648438</v>
@@ -3141,13 +3164,13 @@
         <v>103.801000213623</v>
       </c>
       <c r="O20">
-        <v>99.82160018920898</v>
+        <v>99.821600189208979</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
       </c>
       <c r="Q20">
-        <v>92.5909502029419</v>
+        <v>92.590950202941897</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3174,7 +3197,7 @@
         <v>114.82</v>
       </c>
       <c r="AA20">
-        <v>79.98999999999999</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="AB20">
         <v>42.92</v>
@@ -3219,7 +3242,7 @@
         <v>1.26</v>
       </c>
       <c r="AP20">
-        <v>13.75911438440007</v>
+        <v>13.759114384400069</v>
       </c>
     </row>
     <row r="21" spans="1:42">
@@ -3227,10 +3250,10 @@
         <v>61</v>
       </c>
       <c r="B21">
-        <v>92.2465208747515</v>
+        <v>92.246520874751496</v>
       </c>
       <c r="C21">
-        <v>77.93240556660039</v>
+        <v>77.932405566600394</v>
       </c>
       <c r="D21">
         <v>356</v>
@@ -3242,16 +3265,16 @@
         <v>395.81</v>
       </c>
       <c r="G21">
-        <v>0.3585984546168772</v>
+        <v>0.35859845461687723</v>
       </c>
       <c r="H21">
-        <v>0.827396657380299</v>
+        <v>0.82739665738029899</v>
       </c>
       <c r="I21">
         <v>1.59</v>
       </c>
       <c r="J21">
-        <v>-0.4861720749207691</v>
+        <v>-0.48617207492076908</v>
       </c>
       <c r="K21">
         <v>2.85</v>
@@ -3260,19 +3283,19 @@
         <v>-0.1092276929324212</v>
       </c>
       <c r="M21">
-        <v>406.1219970703125</v>
+        <v>406.12199707031249</v>
       </c>
       <c r="N21">
-        <v>406.8514999389648</v>
+        <v>406.85149993896482</v>
       </c>
       <c r="O21">
-        <v>376.0383978271485</v>
+        <v>376.03839782714851</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
       </c>
       <c r="Q21">
-        <v>359.7987986755371</v>
+        <v>359.79879867553711</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3281,7 +3304,7 @@
         <v>1.08</v>
       </c>
       <c r="U21">
-        <v>8.333333333333332</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="V21" t="b">
         <v>0</v>
@@ -3302,7 +3325,7 @@
         <v>56.27</v>
       </c>
       <c r="AB21">
-        <v>36.23</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="AC21">
         <v>6.81</v>
@@ -3344,7 +3367,7 @@
         <v>2.73</v>
       </c>
       <c r="AP21">
-        <v>11.76762675342371</v>
+        <v>11.767626753423709</v>
       </c>
     </row>
     <row r="22" spans="1:42">
@@ -3352,7 +3375,7 @@
         <v>62</v>
       </c>
       <c r="B22">
-        <v>95.82504970178927</v>
+        <v>95.825049701789268</v>
       </c>
       <c r="C22">
         <v>88.66799204771371</v>
@@ -3367,16 +3390,16 @@
         <v>268.68</v>
       </c>
       <c r="G22">
-        <v>0.5017795410669474</v>
+        <v>0.50177954106694744</v>
       </c>
       <c r="H22">
-        <v>0.4628676648666858</v>
+        <v>0.46286766486668579</v>
       </c>
       <c r="I22">
         <v>1.2</v>
       </c>
       <c r="J22">
-        <v>-0.8388638703432025</v>
+        <v>-0.83886387034320253</v>
       </c>
       <c r="K22">
         <v>1.82</v>
@@ -3388,7 +3411,7 @@
         <v>273.8</v>
       </c>
       <c r="N22">
-        <v>279.7845001220703</v>
+        <v>279.78450012207031</v>
       </c>
       <c r="O22">
         <v>262.5429995727539</v>
@@ -3397,7 +3420,7 @@
         <v>1</v>
       </c>
       <c r="Q22">
-        <v>214.7296003723145</v>
+        <v>214.72960037231451</v>
       </c>
       <c r="R22">
         <v>0.98</v>
@@ -3427,16 +3450,16 @@
         <v>25.27</v>
       </c>
       <c r="AB22">
-        <v>9.220000000000001</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="AC22">
         <v>9.82</v>
       </c>
       <c r="AD22">
-        <v>9.279999999999999</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="AE22">
-        <v>-9.779999999999999</v>
+        <v>-9.7799999999999994</v>
       </c>
       <c r="AF22">
         <v>-3.38</v>
@@ -3445,7 +3468,7 @@
         <v>2.99</v>
       </c>
       <c r="AH22">
-        <v>4.15</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="AI22" t="s">
         <v>81</v>
@@ -3477,10 +3500,10 @@
         <v>63</v>
       </c>
       <c r="B23">
-        <v>90.05964214711729</v>
+        <v>90.059642147117287</v>
       </c>
       <c r="C23">
-        <v>63.81709741550696</v>
+        <v>63.817097415506957</v>
       </c>
       <c r="D23">
         <v>126</v>
@@ -3501,28 +3524,28 @@
         <v>2.38</v>
       </c>
       <c r="J23">
-        <v>0.2282548952939031</v>
+        <v>0.22825489529390311</v>
       </c>
       <c r="K23">
         <v>3.62</v>
       </c>
       <c r="L23">
-        <v>0.6285383031900736</v>
+        <v>0.62853830319007364</v>
       </c>
       <c r="M23">
-        <v>189.5059997558594</v>
+        <v>189.50599975585939</v>
       </c>
       <c r="N23">
-        <v>191.3119995117187</v>
+        <v>191.31199951171871</v>
       </c>
       <c r="O23">
-        <v>179.545400390625</v>
+        <v>179.54540039062499</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
       <c r="Q23">
-        <v>173.965549697876</v>
+        <v>173.96554969787601</v>
       </c>
       <c r="R23">
         <v>0.99</v>
@@ -3543,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="Y23">
-        <v>128.23</v>
+        <v>128.22999999999999</v>
       </c>
       <c r="Z23">
         <v>210.67</v>
@@ -3594,7 +3617,7 @@
         <v>31.82</v>
       </c>
       <c r="AP23">
-        <v>10.28456530086429</v>
+        <v>10.284565300864291</v>
       </c>
     </row>
     <row r="24" spans="1:42">
@@ -3602,10 +3625,10 @@
         <v>64</v>
       </c>
       <c r="B24">
-        <v>94.03578528827038</v>
+        <v>94.035785288270375</v>
       </c>
       <c r="C24">
-        <v>75.94433399602386</v>
+        <v>75.944333996023857</v>
       </c>
       <c r="D24">
         <v>68</v>
@@ -3617,28 +3640,28 @@
         <v>60.27</v>
       </c>
       <c r="G24">
-        <v>0.3922060478984306</v>
+        <v>0.39220604789843061</v>
       </c>
       <c r="H24">
-        <v>0.7089985082000921</v>
+        <v>0.70899850820009214</v>
       </c>
       <c r="I24">
         <v>1.41</v>
       </c>
       <c r="J24">
-        <v>-0.648952903577277</v>
+        <v>-0.64895290357727697</v>
       </c>
       <c r="K24">
         <v>1.95</v>
       </c>
       <c r="L24">
-        <v>-0.9715515845041686</v>
+        <v>-0.97155158450416856</v>
       </c>
       <c r="M24">
-        <v>59.54599990844726</v>
+        <v>59.545999908447257</v>
       </c>
       <c r="N24">
-        <v>58.76300010681152</v>
+        <v>58.763000106811518</v>
       </c>
       <c r="O24">
         <v>58.5905997467041</v>
@@ -3647,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="Q24">
-        <v>54.22739997863769</v>
+        <v>54.227399978637692</v>
       </c>
       <c r="R24">
         <v>1.01</v>
@@ -3683,13 +3706,13 @@
         <v>13.33</v>
       </c>
       <c r="AD24">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="AE24">
         <v>18.32</v>
       </c>
       <c r="AG24">
-        <v>75.76000000000001</v>
+        <v>75.760000000000005</v>
       </c>
       <c r="AH24">
         <v>-36.54</v>
@@ -3724,7 +3747,7 @@
         <v>65</v>
       </c>
       <c r="B25">
-        <v>93.63817097415506</v>
+        <v>93.638170974155059</v>
       </c>
       <c r="C25">
         <v>61.82902584493042</v>
@@ -3739,7 +3762,7 @@
         <v>149.63</v>
       </c>
       <c r="G25">
-        <v>0.3976487685843595</v>
+        <v>0.39764876858435949</v>
       </c>
       <c r="H25">
         <v>1.052623614230296</v>
@@ -3748,22 +3771,22 @@
         <v>1.95</v>
       </c>
       <c r="J25">
-        <v>-0.160610417607754</v>
+        <v>-0.16061041760775399</v>
       </c>
       <c r="K25">
         <v>2.72</v>
       </c>
       <c r="L25">
-        <v>-0.2337855883816735</v>
+        <v>-0.23378558838167349</v>
       </c>
       <c r="M25">
         <v>149.0360015869141</v>
       </c>
       <c r="N25">
-        <v>146.7415008544922</v>
+        <v>146.74150085449219</v>
       </c>
       <c r="O25">
-        <v>142.7202008056641</v>
+        <v>142.72020080566409</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -3790,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>96.76000000000001</v>
+        <v>96.76</v>
       </c>
       <c r="Z25">
         <v>156.35</v>
@@ -3832,7 +3855,7 @@
         <v>114</v>
       </c>
       <c r="AM25">
-        <v>8.039999999999999</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="AN25">
         <v>7.9</v>
@@ -3841,7 +3864,7 @@
         <v>-1.74</v>
       </c>
       <c r="AP25">
-        <v>10.03801212663022</v>
+        <v>10.038012126630219</v>
       </c>
     </row>
     <row r="26" spans="1:42">
@@ -3849,10 +3872,10 @@
         <v>66</v>
       </c>
       <c r="B26">
-        <v>91.65009940357854</v>
+        <v>91.650099403578537</v>
       </c>
       <c r="C26">
-        <v>85.08946322067594</v>
+        <v>85.089463220675938</v>
       </c>
       <c r="D26">
         <v>316</v>
@@ -3864,7 +3887,7 @@
         <v>213.71</v>
       </c>
       <c r="G26">
-        <v>0.3528810658085202</v>
+        <v>0.35288106580852019</v>
       </c>
       <c r="H26">
         <v>0.688439776316497</v>
@@ -3873,28 +3896,28 @@
         <v>1.6</v>
       </c>
       <c r="J26">
-        <v>-0.4771286955509632</v>
+        <v>-0.47712869555096321</v>
       </c>
       <c r="K26">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="L26">
-        <v>-0.8949005719200134</v>
+        <v>-0.89490057192001338</v>
       </c>
       <c r="M26">
         <v>209.8840026855469</v>
       </c>
       <c r="N26">
-        <v>205.2794998168945</v>
+        <v>205.27949981689451</v>
       </c>
       <c r="O26">
-        <v>202.1019998168945</v>
+        <v>202.10199981689451</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
       </c>
       <c r="Q26">
-        <v>180.5538502502442</v>
+        <v>180.55385025024421</v>
       </c>
       <c r="R26">
         <v>1.02</v>
@@ -3903,7 +3926,7 @@
         <v>1.02</v>
       </c>
       <c r="U26">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="V26" t="b">
         <v>0</v>
@@ -3924,7 +3947,7 @@
         <v>25.02</v>
       </c>
       <c r="AB26">
-        <v>8.380000000000001</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="AC26">
         <v>6.95</v>
@@ -3957,7 +3980,7 @@
         <v>114</v>
       </c>
       <c r="AM26">
-        <v>8.869999999999999</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="AN26">
         <v>10.56</v>
@@ -3966,10 +3989,11 @@
         <v>19.05</v>
       </c>
       <c r="AP26">
-        <v>4.27301640298455</v>
+        <v>4.2730164029845499</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>